--- a/docs/dataset/CAMRI_ARB_Test_Dataset.xlsx
+++ b/docs/dataset/CAMRI_ARB_Test_Dataset.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ARB Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARB Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L122"/>
+  <dimension ref="A1:P122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -517,6 +517,26 @@
           <t>CFU/mL</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>CFU/mL</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>CFU/mL</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>CFU/mL</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>CFU/mL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -579,6 +599,26 @@
           <t>Ec_MEM</t>
         </is>
       </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Ec</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Ent</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Kleb</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Pseu</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -629,6 +669,18 @@
       <c r="L3" t="n">
         <v>6044.4</v>
       </c>
+      <c r="M3" t="n">
+        <v>162.25</v>
+      </c>
+      <c r="N3" t="n">
+        <v>196.49</v>
+      </c>
+      <c r="O3" t="n">
+        <v>130.05</v>
+      </c>
+      <c r="P3" t="n">
+        <v>134.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -679,6 +731,18 @@
       <c r="L4" t="n">
         <v>1390.2</v>
       </c>
+      <c r="M4" t="n">
+        <v>75.84999999999999</v>
+      </c>
+      <c r="N4" t="n">
+        <v>199.79</v>
+      </c>
+      <c r="O4" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>65.05</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -729,6 +793,18 @@
       <c r="L5" t="n">
         <v>618</v>
       </c>
+      <c r="M5" t="n">
+        <v>325.64</v>
+      </c>
+      <c r="N5" t="n">
+        <v>52.22</v>
+      </c>
+      <c r="O5" t="n">
+        <v>65.97</v>
+      </c>
+      <c r="P5" t="n">
+        <v>263.69</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -779,6 +855,18 @@
       <c r="L6" t="n">
         <v>4609.8</v>
       </c>
+      <c r="M6" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="N6" t="n">
+        <v>317.33</v>
+      </c>
+      <c r="O6" t="n">
+        <v>455.05</v>
+      </c>
+      <c r="P6" t="n">
+        <v>119.6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -829,6 +917,18 @@
       <c r="L7" t="n">
         <v>1097.6</v>
       </c>
+      <c r="M7" t="n">
+        <v>268.17</v>
+      </c>
+      <c r="N7" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="O7" t="n">
+        <v>177.22</v>
+      </c>
+      <c r="P7" t="n">
+        <v>55.17</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -879,6 +979,18 @@
       <c r="L8" t="n">
         <v>331.8</v>
       </c>
+      <c r="M8" t="n">
+        <v>183.16</v>
+      </c>
+      <c r="N8" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="O8" t="n">
+        <v>229.35</v>
+      </c>
+      <c r="P8" t="n">
+        <v>81.14</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -929,6 +1041,18 @@
       <c r="L9" t="n">
         <v>2110.7</v>
       </c>
+      <c r="M9" t="n">
+        <v>29.47</v>
+      </c>
+      <c r="N9" t="n">
+        <v>104.78</v>
+      </c>
+      <c r="O9" t="n">
+        <v>291.88</v>
+      </c>
+      <c r="P9" t="n">
+        <v>25.66</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -979,6 +1103,18 @@
       <c r="L10" t="n">
         <v>12596.5</v>
       </c>
+      <c r="M10" t="n">
+        <v>253.96</v>
+      </c>
+      <c r="N10" t="n">
+        <v>81.56999999999999</v>
+      </c>
+      <c r="O10" t="n">
+        <v>452.2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>101.28</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1029,6 +1165,18 @@
       <c r="L11" t="n">
         <v>6224.6</v>
       </c>
+      <c r="M11" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="N11" t="n">
+        <v>170.36</v>
+      </c>
+      <c r="O11" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>156.34</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1079,6 +1227,18 @@
       <c r="L12" t="n">
         <v>3680.6</v>
       </c>
+      <c r="M12" t="n">
+        <v>217.11</v>
+      </c>
+      <c r="N12" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="O12" t="n">
+        <v>458.9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>152.85</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1129,6 +1289,18 @@
       <c r="L13" t="n">
         <v>7.3</v>
       </c>
+      <c r="M13" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O13" t="n">
+        <v>251.07</v>
+      </c>
+      <c r="P13" t="n">
+        <v>379.87</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1179,6 +1351,18 @@
       <c r="L14" t="n">
         <v>7357.7</v>
       </c>
+      <c r="M14" t="n">
+        <v>45.81</v>
+      </c>
+      <c r="N14" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="O14" t="n">
+        <v>266.15</v>
+      </c>
+      <c r="P14" t="n">
+        <v>145.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1229,6 +1413,18 @@
       <c r="L15" t="n">
         <v>2675.4</v>
       </c>
+      <c r="M15" t="n">
+        <v>212.55</v>
+      </c>
+      <c r="N15" t="n">
+        <v>51.18</v>
+      </c>
+      <c r="O15" t="n">
+        <v>261.99</v>
+      </c>
+      <c r="P15" t="n">
+        <v>250.29</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1279,6 +1475,18 @@
       <c r="L16" t="n">
         <v>959.3</v>
       </c>
+      <c r="M16" t="n">
+        <v>413.51</v>
+      </c>
+      <c r="N16" t="n">
+        <v>182.12</v>
+      </c>
+      <c r="O16" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="P16" t="n">
+        <v>89.36</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1329,6 +1537,18 @@
       <c r="L17" t="n">
         <v>5315</v>
       </c>
+      <c r="M17" t="n">
+        <v>62.34</v>
+      </c>
+      <c r="N17" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="O17" t="n">
+        <v>220.34</v>
+      </c>
+      <c r="P17" t="n">
+        <v>173.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1379,6 +1599,18 @@
       <c r="L18" t="n">
         <v>11156.1</v>
       </c>
+      <c r="M18" t="n">
+        <v>112.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>437.23</v>
+      </c>
+      <c r="O18" t="n">
+        <v>91.95999999999999</v>
+      </c>
+      <c r="P18" t="n">
+        <v>9.57</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1429,6 +1661,18 @@
       <c r="L19" t="n">
         <v>1807.6</v>
       </c>
+      <c r="M19" t="n">
+        <v>313.9</v>
+      </c>
+      <c r="N19" t="n">
+        <v>307.23</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P19" t="n">
+        <v>125.6</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1479,6 +1723,18 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>473.88</v>
+      </c>
+      <c r="N20" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>399.69</v>
+      </c>
+      <c r="P20" t="n">
+        <v>8.17</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1529,6 +1785,18 @@
       <c r="L21" t="n">
         <v>76.7</v>
       </c>
+      <c r="M21" t="n">
+        <v>288.76</v>
+      </c>
+      <c r="N21" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>86.59</v>
+      </c>
+      <c r="P21" t="n">
+        <v>366.67</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1579,6 +1847,18 @@
       <c r="L22" t="n">
         <v>4495.4</v>
       </c>
+      <c r="M22" t="n">
+        <v>198.64</v>
+      </c>
+      <c r="N22" t="n">
+        <v>174.02</v>
+      </c>
+      <c r="O22" t="n">
+        <v>237.01</v>
+      </c>
+      <c r="P22" t="n">
+        <v>275.75</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1629,6 +1909,18 @@
       <c r="L23" t="n">
         <v>8302.299999999999</v>
       </c>
+      <c r="M23" t="n">
+        <v>488.14</v>
+      </c>
+      <c r="N23" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>362.73</v>
+      </c>
+      <c r="P23" t="n">
+        <v>95.13</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1679,6 +1971,18 @@
       <c r="L24" t="n">
         <v>1326.5</v>
       </c>
+      <c r="M24" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="N24" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="O24" t="n">
+        <v>278.46</v>
+      </c>
+      <c r="P24" t="n">
+        <v>237.64</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1729,6 +2033,18 @@
       <c r="L25" t="n">
         <v>297.9</v>
       </c>
+      <c r="M25" t="n">
+        <v>429.3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>424.54</v>
+      </c>
+      <c r="O25" t="n">
+        <v>163.33</v>
+      </c>
+      <c r="P25" t="n">
+        <v>467.35</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1779,6 +2095,18 @@
       <c r="L26" t="n">
         <v>11031.3</v>
       </c>
+      <c r="M26" t="n">
+        <v>145.16</v>
+      </c>
+      <c r="N26" t="n">
+        <v>496.55</v>
+      </c>
+      <c r="O26" t="n">
+        <v>259.42</v>
+      </c>
+      <c r="P26" t="n">
+        <v>53.59</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1829,6 +2157,18 @@
       <c r="L27" t="n">
         <v>3054.3</v>
       </c>
+      <c r="M27" t="n">
+        <v>72.56</v>
+      </c>
+      <c r="N27" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="O27" t="n">
+        <v>277.94</v>
+      </c>
+      <c r="P27" t="n">
+        <v>409.55</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1879,6 +2219,18 @@
       <c r="L28" t="n">
         <v>527.5</v>
       </c>
+      <c r="M28" t="n">
+        <v>59.34</v>
+      </c>
+      <c r="N28" t="n">
+        <v>242.18</v>
+      </c>
+      <c r="O28" t="n">
+        <v>392.24</v>
+      </c>
+      <c r="P28" t="n">
+        <v>216.37</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1929,6 +2281,18 @@
       <c r="L29" t="n">
         <v>6182.7</v>
       </c>
+      <c r="M29" t="n">
+        <v>154.59</v>
+      </c>
+      <c r="N29" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="O29" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="P29" t="n">
+        <v>247.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1979,6 +2343,18 @@
       <c r="L30" t="n">
         <v>26.8</v>
       </c>
+      <c r="M30" t="n">
+        <v>408.16</v>
+      </c>
+      <c r="N30" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="O30" t="n">
+        <v>280.37</v>
+      </c>
+      <c r="P30" t="n">
+        <v>417.39</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2029,6 +2405,18 @@
       <c r="L31" t="n">
         <v>0</v>
       </c>
+      <c r="M31" t="n">
+        <v>90.77</v>
+      </c>
+      <c r="N31" t="n">
+        <v>171.65</v>
+      </c>
+      <c r="O31" t="n">
+        <v>124.62</v>
+      </c>
+      <c r="P31" t="n">
+        <v>196.85</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2079,6 +2467,18 @@
       <c r="L32" t="n">
         <v>1934.1</v>
       </c>
+      <c r="M32" t="n">
+        <v>291.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>132.75</v>
+      </c>
+      <c r="O32" t="n">
+        <v>138.82</v>
+      </c>
+      <c r="P32" t="n">
+        <v>253.59</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2129,6 +2529,18 @@
       <c r="L33" t="n">
         <v>11826.4</v>
       </c>
+      <c r="M33" t="n">
+        <v>319.64</v>
+      </c>
+      <c r="N33" t="n">
+        <v>414.51</v>
+      </c>
+      <c r="O33" t="n">
+        <v>386.24</v>
+      </c>
+      <c r="P33" t="n">
+        <v>344.03</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2179,6 +2591,18 @@
       <c r="L34" t="n">
         <v>1889.2</v>
       </c>
+      <c r="M34" t="n">
+        <v>186.51</v>
+      </c>
+      <c r="N34" t="n">
+        <v>81.14</v>
+      </c>
+      <c r="O34" t="n">
+        <v>254.1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>491.23</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2229,6 +2653,18 @@
       <c r="L35" t="n">
         <v>3953.7</v>
       </c>
+      <c r="M35" t="n">
+        <v>274.1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="O35" t="n">
+        <v>281.08</v>
+      </c>
+      <c r="P35" t="n">
+        <v>171.68</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2279,6 +2715,18 @@
       <c r="L36" t="n">
         <v>69.3</v>
       </c>
+      <c r="M36" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="N36" t="n">
+        <v>475.52</v>
+      </c>
+      <c r="O36" t="n">
+        <v>380.12</v>
+      </c>
+      <c r="P36" t="n">
+        <v>416.23</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2329,6 +2777,18 @@
       <c r="L37" t="n">
         <v>2670.4</v>
       </c>
+      <c r="M37" t="n">
+        <v>30.27</v>
+      </c>
+      <c r="N37" t="n">
+        <v>264.36</v>
+      </c>
+      <c r="O37" t="n">
+        <v>456.29</v>
+      </c>
+      <c r="P37" t="n">
+        <v>353.51</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2379,6 +2839,18 @@
       <c r="L38" t="n">
         <v>489.2</v>
       </c>
+      <c r="M38" t="n">
+        <v>103.38</v>
+      </c>
+      <c r="N38" t="n">
+        <v>73.73</v>
+      </c>
+      <c r="O38" t="n">
+        <v>221.9</v>
+      </c>
+      <c r="P38" t="n">
+        <v>318.17</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2429,6 +2901,18 @@
       <c r="L39" t="n">
         <v>6210.2</v>
       </c>
+      <c r="M39" t="n">
+        <v>340.36</v>
+      </c>
+      <c r="N39" t="n">
+        <v>271.81</v>
+      </c>
+      <c r="O39" t="n">
+        <v>306.46</v>
+      </c>
+      <c r="P39" t="n">
+        <v>202.65</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2479,6 +2963,18 @@
       <c r="L40" t="n">
         <v>2670</v>
       </c>
+      <c r="M40" t="n">
+        <v>214.08</v>
+      </c>
+      <c r="N40" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="O40" t="n">
+        <v>253.02</v>
+      </c>
+      <c r="P40" t="n">
+        <v>174.1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2529,6 +3025,18 @@
       <c r="L41" t="n">
         <v>2424</v>
       </c>
+      <c r="M41" t="n">
+        <v>157.42</v>
+      </c>
+      <c r="N41" t="n">
+        <v>264.29</v>
+      </c>
+      <c r="O41" t="n">
+        <v>256.32</v>
+      </c>
+      <c r="P41" t="n">
+        <v>27.67</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2579,6 +3087,18 @@
       <c r="L42" t="n">
         <v>0</v>
       </c>
+      <c r="M42" t="n">
+        <v>292.99</v>
+      </c>
+      <c r="N42" t="n">
+        <v>489.26</v>
+      </c>
+      <c r="O42" t="n">
+        <v>346.52</v>
+      </c>
+      <c r="P42" t="n">
+        <v>65.34</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2629,6 +3149,18 @@
       <c r="L43" t="n">
         <v>767</v>
       </c>
+      <c r="M43" t="n">
+        <v>226.87</v>
+      </c>
+      <c r="N43" t="n">
+        <v>431.73</v>
+      </c>
+      <c r="O43" t="n">
+        <v>226.45</v>
+      </c>
+      <c r="P43" t="n">
+        <v>35.83</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2679,6 +3211,18 @@
       <c r="L44" t="n">
         <v>2014.6</v>
       </c>
+      <c r="M44" t="n">
+        <v>150.23</v>
+      </c>
+      <c r="N44" t="n">
+        <v>348.25</v>
+      </c>
+      <c r="O44" t="n">
+        <v>266.88</v>
+      </c>
+      <c r="P44" t="n">
+        <v>370.57</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2729,6 +3273,18 @@
       <c r="L45" t="n">
         <v>3777.2</v>
       </c>
+      <c r="M45" t="n">
+        <v>397.29</v>
+      </c>
+      <c r="N45" t="n">
+        <v>130.93</v>
+      </c>
+      <c r="O45" t="n">
+        <v>239.28</v>
+      </c>
+      <c r="P45" t="n">
+        <v>128.17</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2779,6 +3335,18 @@
       <c r="L46" t="n">
         <v>4229.5</v>
       </c>
+      <c r="M46" t="n">
+        <v>349.65</v>
+      </c>
+      <c r="N46" t="n">
+        <v>183.67</v>
+      </c>
+      <c r="O46" t="n">
+        <v>470.78</v>
+      </c>
+      <c r="P46" t="n">
+        <v>82.04000000000001</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2829,6 +3397,18 @@
       <c r="L47" t="n">
         <v>2701.9</v>
       </c>
+      <c r="M47" t="n">
+        <v>122.43</v>
+      </c>
+      <c r="N47" t="n">
+        <v>83.94</v>
+      </c>
+      <c r="O47" t="n">
+        <v>349.76</v>
+      </c>
+      <c r="P47" t="n">
+        <v>42.7</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2879,6 +3459,18 @@
       <c r="L48" t="n">
         <v>372.3</v>
       </c>
+      <c r="M48" t="n">
+        <v>287.42</v>
+      </c>
+      <c r="N48" t="n">
+        <v>386.08</v>
+      </c>
+      <c r="O48" t="n">
+        <v>438.33</v>
+      </c>
+      <c r="P48" t="n">
+        <v>420.71</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2929,6 +3521,18 @@
       <c r="L49" t="n">
         <v>4702.8</v>
       </c>
+      <c r="M49" t="n">
+        <v>262.84</v>
+      </c>
+      <c r="N49" t="n">
+        <v>266.53</v>
+      </c>
+      <c r="O49" t="n">
+        <v>471.12</v>
+      </c>
+      <c r="P49" t="n">
+        <v>435.33</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2979,6 +3583,18 @@
       <c r="L50" t="n">
         <v>1455.8</v>
       </c>
+      <c r="M50" t="n">
+        <v>437.63</v>
+      </c>
+      <c r="N50" t="n">
+        <v>389.64</v>
+      </c>
+      <c r="O50" t="n">
+        <v>130.17</v>
+      </c>
+      <c r="P50" t="n">
+        <v>335.44</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3029,6 +3645,18 @@
       <c r="L51" t="n">
         <v>3199.3</v>
       </c>
+      <c r="M51" t="n">
+        <v>364.86</v>
+      </c>
+      <c r="N51" t="n">
+        <v>165.17</v>
+      </c>
+      <c r="O51" t="n">
+        <v>279.98</v>
+      </c>
+      <c r="P51" t="n">
+        <v>141.33</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3079,6 +3707,18 @@
       <c r="L52" t="n">
         <v>3873</v>
       </c>
+      <c r="M52" t="n">
+        <v>144.32</v>
+      </c>
+      <c r="N52" t="n">
+        <v>111.91</v>
+      </c>
+      <c r="O52" t="n">
+        <v>471.66</v>
+      </c>
+      <c r="P52" t="n">
+        <v>121.49</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3129,6 +3769,18 @@
       <c r="L53" t="n">
         <v>6309.6</v>
       </c>
+      <c r="M53" t="n">
+        <v>490.1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>405.85</v>
+      </c>
+      <c r="O53" t="n">
+        <v>420.08</v>
+      </c>
+      <c r="P53" t="n">
+        <v>146.88</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3179,6 +3831,18 @@
       <c r="L54" t="n">
         <v>111.6</v>
       </c>
+      <c r="M54" t="n">
+        <v>59.47</v>
+      </c>
+      <c r="N54" t="n">
+        <v>492.47</v>
+      </c>
+      <c r="O54" t="n">
+        <v>69</v>
+      </c>
+      <c r="P54" t="n">
+        <v>230</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3229,6 +3893,18 @@
       <c r="L55" t="n">
         <v>872.6</v>
       </c>
+      <c r="M55" t="n">
+        <v>209.35</v>
+      </c>
+      <c r="N55" t="n">
+        <v>426.39</v>
+      </c>
+      <c r="O55" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="P55" t="n">
+        <v>79.19</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3279,6 +3955,18 @@
       <c r="L56" t="n">
         <v>2366.2</v>
       </c>
+      <c r="M56" t="n">
+        <v>378.69</v>
+      </c>
+      <c r="N56" t="n">
+        <v>403.14</v>
+      </c>
+      <c r="O56" t="n">
+        <v>221.34</v>
+      </c>
+      <c r="P56" t="n">
+        <v>223.19</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3329,6 +4017,18 @@
       <c r="L57" t="n">
         <v>3311.1</v>
       </c>
+      <c r="M57" t="n">
+        <v>76.42</v>
+      </c>
+      <c r="N57" t="n">
+        <v>409.26</v>
+      </c>
+      <c r="O57" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="P57" t="n">
+        <v>131.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3379,6 +4079,18 @@
       <c r="L58" t="n">
         <v>3724.2</v>
       </c>
+      <c r="M58" t="n">
+        <v>244.74</v>
+      </c>
+      <c r="N58" t="n">
+        <v>370.07</v>
+      </c>
+      <c r="O58" t="n">
+        <v>120.7</v>
+      </c>
+      <c r="P58" t="n">
+        <v>480.91</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3429,6 +4141,18 @@
       <c r="L59" t="n">
         <v>421.1</v>
       </c>
+      <c r="M59" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="N59" t="n">
+        <v>113.76</v>
+      </c>
+      <c r="O59" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="P59" t="n">
+        <v>486.33</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3479,6 +4203,18 @@
       <c r="L60" t="n">
         <v>910.8</v>
       </c>
+      <c r="M60" t="n">
+        <v>334.27</v>
+      </c>
+      <c r="N60" t="n">
+        <v>259.06</v>
+      </c>
+      <c r="O60" t="n">
+        <v>334.9</v>
+      </c>
+      <c r="P60" t="n">
+        <v>273.76</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3529,6 +4265,18 @@
       <c r="L61" t="n">
         <v>3813.2</v>
       </c>
+      <c r="M61" t="n">
+        <v>382.4</v>
+      </c>
+      <c r="N61" t="n">
+        <v>178.1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>392.08</v>
+      </c>
+      <c r="P61" t="n">
+        <v>122.6</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3579,6 +4327,18 @@
       <c r="L62" t="n">
         <v>2271</v>
       </c>
+      <c r="M62" t="n">
+        <v>286.73</v>
+      </c>
+      <c r="N62" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="O62" t="n">
+        <v>448.56</v>
+      </c>
+      <c r="P62" t="n">
+        <v>482.85</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3629,6 +4389,18 @@
       <c r="L63" t="n">
         <v>212.6</v>
       </c>
+      <c r="M63" t="n">
+        <v>437.8</v>
+      </c>
+      <c r="N63" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="O63" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="P63" t="n">
+        <v>155.12</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3679,6 +4451,18 @@
       <c r="L64" t="n">
         <v>492.2</v>
       </c>
+      <c r="M64" t="n">
+        <v>157.22</v>
+      </c>
+      <c r="N64" t="n">
+        <v>140.07</v>
+      </c>
+      <c r="O64" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="P64" t="n">
+        <v>178.61</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3729,6 +4513,18 @@
       <c r="L65" t="n">
         <v>1154.4</v>
       </c>
+      <c r="M65" t="n">
+        <v>347.8</v>
+      </c>
+      <c r="N65" t="n">
+        <v>129.96</v>
+      </c>
+      <c r="O65" t="n">
+        <v>330.3</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1.03</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3779,6 +4575,18 @@
       <c r="L66" t="n">
         <v>5124.7</v>
       </c>
+      <c r="M66" t="n">
+        <v>297.39</v>
+      </c>
+      <c r="N66" t="n">
+        <v>346.41</v>
+      </c>
+      <c r="O66" t="n">
+        <v>71.92</v>
+      </c>
+      <c r="P66" t="n">
+        <v>191.12</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3829,6 +4637,18 @@
       <c r="L67" t="n">
         <v>3209.6</v>
       </c>
+      <c r="M67" t="n">
+        <v>290.16</v>
+      </c>
+      <c r="N67" t="n">
+        <v>478.28</v>
+      </c>
+      <c r="O67" t="n">
+        <v>441.48</v>
+      </c>
+      <c r="P67" t="n">
+        <v>237.58</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3879,6 +4699,18 @@
       <c r="L68" t="n">
         <v>7666.2</v>
       </c>
+      <c r="M68" t="n">
+        <v>228.37</v>
+      </c>
+      <c r="N68" t="n">
+        <v>223.89</v>
+      </c>
+      <c r="O68" t="n">
+        <v>483.79</v>
+      </c>
+      <c r="P68" t="n">
+        <v>251.63</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3929,6 +4761,18 @@
       <c r="L69" t="n">
         <v>4514.2</v>
       </c>
+      <c r="M69" t="n">
+        <v>420.06</v>
+      </c>
+      <c r="N69" t="n">
+        <v>468.54</v>
+      </c>
+      <c r="O69" t="n">
+        <v>110.18</v>
+      </c>
+      <c r="P69" t="n">
+        <v>100.89</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3979,6 +4823,18 @@
       <c r="L70" t="n">
         <v>398.4</v>
       </c>
+      <c r="M70" t="n">
+        <v>472.37</v>
+      </c>
+      <c r="N70" t="n">
+        <v>494.03</v>
+      </c>
+      <c r="O70" t="n">
+        <v>476.28</v>
+      </c>
+      <c r="P70" t="n">
+        <v>252.62</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4029,6 +4885,18 @@
       <c r="L71" t="n">
         <v>2379.6</v>
       </c>
+      <c r="M71" t="n">
+        <v>237.31</v>
+      </c>
+      <c r="N71" t="n">
+        <v>477.52</v>
+      </c>
+      <c r="O71" t="n">
+        <v>199.43</v>
+      </c>
+      <c r="P71" t="n">
+        <v>2.97</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4079,6 +4947,18 @@
       <c r="L72" t="n">
         <v>6785.3</v>
       </c>
+      <c r="M72" t="n">
+        <v>332.24</v>
+      </c>
+      <c r="N72" t="n">
+        <v>182.64</v>
+      </c>
+      <c r="O72" t="n">
+        <v>243.89</v>
+      </c>
+      <c r="P72" t="n">
+        <v>132.45</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4129,6 +5009,18 @@
       <c r="L73" t="n">
         <v>13773.2</v>
       </c>
+      <c r="M73" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="N73" t="n">
+        <v>110.62</v>
+      </c>
+      <c r="O73" t="n">
+        <v>494.94</v>
+      </c>
+      <c r="P73" t="n">
+        <v>45.33</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4179,6 +5071,18 @@
       <c r="L74" t="n">
         <v>482.2</v>
       </c>
+      <c r="M74" t="n">
+        <v>350.9</v>
+      </c>
+      <c r="N74" t="n">
+        <v>113.81</v>
+      </c>
+      <c r="O74" t="n">
+        <v>416.31</v>
+      </c>
+      <c r="P74" t="n">
+        <v>200.06</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4229,6 +5133,18 @@
       <c r="L75" t="n">
         <v>279.9</v>
       </c>
+      <c r="M75" t="n">
+        <v>323.74</v>
+      </c>
+      <c r="N75" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="O75" t="n">
+        <v>81.15000000000001</v>
+      </c>
+      <c r="P75" t="n">
+        <v>21.31</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4279,6 +5195,18 @@
       <c r="L76" t="n">
         <v>0</v>
       </c>
+      <c r="M76" t="n">
+        <v>496.55</v>
+      </c>
+      <c r="N76" t="n">
+        <v>102.58</v>
+      </c>
+      <c r="O76" t="n">
+        <v>216.05</v>
+      </c>
+      <c r="P76" t="n">
+        <v>11.74</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4329,6 +5257,18 @@
       <c r="L77" t="n">
         <v>11092.7</v>
       </c>
+      <c r="M77" t="n">
+        <v>411.05</v>
+      </c>
+      <c r="N77" t="n">
+        <v>312.22</v>
+      </c>
+      <c r="O77" t="n">
+        <v>258.04</v>
+      </c>
+      <c r="P77" t="n">
+        <v>152.47</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4379,6 +5319,18 @@
       <c r="L78" t="n">
         <v>703.2</v>
       </c>
+      <c r="M78" t="n">
+        <v>142.66</v>
+      </c>
+      <c r="N78" t="n">
+        <v>450.2</v>
+      </c>
+      <c r="O78" t="n">
+        <v>169.89</v>
+      </c>
+      <c r="P78" t="n">
+        <v>116.79</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4429,6 +5381,18 @@
       <c r="L79" t="n">
         <v>782.5</v>
       </c>
+      <c r="M79" t="n">
+        <v>193.2</v>
+      </c>
+      <c r="N79" t="n">
+        <v>420.3</v>
+      </c>
+      <c r="O79" t="n">
+        <v>98.27</v>
+      </c>
+      <c r="P79" t="n">
+        <v>293</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4479,6 +5443,18 @@
       <c r="L80" t="n">
         <v>265.6</v>
       </c>
+      <c r="M80" t="n">
+        <v>334.49</v>
+      </c>
+      <c r="N80" t="n">
+        <v>240</v>
+      </c>
+      <c r="O80" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="P80" t="n">
+        <v>264.83</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4529,6 +5505,18 @@
       <c r="L81" t="n">
         <v>374.1</v>
       </c>
+      <c r="M81" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="N81" t="n">
+        <v>326.66</v>
+      </c>
+      <c r="O81" t="n">
+        <v>361.21</v>
+      </c>
+      <c r="P81" t="n">
+        <v>375.4</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4579,6 +5567,18 @@
       <c r="L82" t="n">
         <v>403.5</v>
       </c>
+      <c r="M82" t="n">
+        <v>231.12</v>
+      </c>
+      <c r="N82" t="n">
+        <v>399.92</v>
+      </c>
+      <c r="O82" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="P82" t="n">
+        <v>328.94</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4629,6 +5629,18 @@
       <c r="L83" t="n">
         <v>334.1</v>
       </c>
+      <c r="M83" t="n">
+        <v>84.44</v>
+      </c>
+      <c r="N83" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="O83" t="n">
+        <v>277.25</v>
+      </c>
+      <c r="P83" t="n">
+        <v>358.14</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4679,6 +5691,18 @@
       <c r="L84" t="n">
         <v>511.8</v>
       </c>
+      <c r="M84" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="N84" t="n">
+        <v>330.46</v>
+      </c>
+      <c r="O84" t="n">
+        <v>220.51</v>
+      </c>
+      <c r="P84" t="n">
+        <v>439.61</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4729,6 +5753,18 @@
       <c r="L85" t="n">
         <v>5349</v>
       </c>
+      <c r="M85" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="N85" t="n">
+        <v>454.93</v>
+      </c>
+      <c r="O85" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="P85" t="n">
+        <v>195.06</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4779,6 +5815,18 @@
       <c r="L86" t="n">
         <v>5630.9</v>
       </c>
+      <c r="M86" t="n">
+        <v>384.23</v>
+      </c>
+      <c r="N86" t="n">
+        <v>391.26</v>
+      </c>
+      <c r="O86" t="n">
+        <v>166.08</v>
+      </c>
+      <c r="P86" t="n">
+        <v>163.4</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4829,6 +5877,18 @@
       <c r="L87" t="n">
         <v>2574</v>
       </c>
+      <c r="M87" t="n">
+        <v>65.11</v>
+      </c>
+      <c r="N87" t="n">
+        <v>375.2</v>
+      </c>
+      <c r="O87" t="n">
+        <v>312.15</v>
+      </c>
+      <c r="P87" t="n">
+        <v>492.37</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4879,6 +5939,18 @@
       <c r="L88" t="n">
         <v>3956.6</v>
       </c>
+      <c r="M88" t="n">
+        <v>124.18</v>
+      </c>
+      <c r="N88" t="n">
+        <v>239.28</v>
+      </c>
+      <c r="O88" t="n">
+        <v>256.38</v>
+      </c>
+      <c r="P88" t="n">
+        <v>75.16</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4929,6 +6001,18 @@
       <c r="L89" t="n">
         <v>198.8</v>
       </c>
+      <c r="M89" t="n">
+        <v>195.78</v>
+      </c>
+      <c r="N89" t="n">
+        <v>89.67</v>
+      </c>
+      <c r="O89" t="n">
+        <v>32.61</v>
+      </c>
+      <c r="P89" t="n">
+        <v>362.22</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4979,6 +6063,18 @@
       <c r="L90" t="n">
         <v>6380.4</v>
       </c>
+      <c r="M90" t="n">
+        <v>435.78</v>
+      </c>
+      <c r="N90" t="n">
+        <v>394.67</v>
+      </c>
+      <c r="O90" t="n">
+        <v>492.55</v>
+      </c>
+      <c r="P90" t="n">
+        <v>321.79</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5029,6 +6125,18 @@
       <c r="L91" t="n">
         <v>10779.1</v>
       </c>
+      <c r="M91" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="N91" t="n">
+        <v>166.59</v>
+      </c>
+      <c r="O91" t="n">
+        <v>394.29</v>
+      </c>
+      <c r="P91" t="n">
+        <v>22.37</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5079,6 +6187,18 @@
       <c r="L92" t="n">
         <v>6122.8</v>
       </c>
+      <c r="M92" t="n">
+        <v>224.87</v>
+      </c>
+      <c r="N92" t="n">
+        <v>400.51</v>
+      </c>
+      <c r="O92" t="n">
+        <v>485.86</v>
+      </c>
+      <c r="P92" t="n">
+        <v>417.73</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5129,6 +6249,18 @@
       <c r="L93" t="n">
         <v>4747.6</v>
       </c>
+      <c r="M93" t="n">
+        <v>274.95</v>
+      </c>
+      <c r="N93" t="n">
+        <v>485.84</v>
+      </c>
+      <c r="O93" t="n">
+        <v>52.84</v>
+      </c>
+      <c r="P93" t="n">
+        <v>446.03</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5179,6 +6311,18 @@
       <c r="L94" t="n">
         <v>4802.8</v>
       </c>
+      <c r="M94" t="n">
+        <v>441.75</v>
+      </c>
+      <c r="N94" t="n">
+        <v>198.22</v>
+      </c>
+      <c r="O94" t="n">
+        <v>133.15</v>
+      </c>
+      <c r="P94" t="n">
+        <v>313.85</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5229,6 +6373,18 @@
       <c r="L95" t="n">
         <v>4993.2</v>
       </c>
+      <c r="M95" t="n">
+        <v>409.73</v>
+      </c>
+      <c r="N95" t="n">
+        <v>200.99</v>
+      </c>
+      <c r="O95" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="P95" t="n">
+        <v>367.06</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5279,6 +6435,18 @@
       <c r="L96" t="n">
         <v>275.4</v>
       </c>
+      <c r="M96" t="n">
+        <v>432.06</v>
+      </c>
+      <c r="N96" t="n">
+        <v>473.43</v>
+      </c>
+      <c r="O96" t="n">
+        <v>389.61</v>
+      </c>
+      <c r="P96" t="n">
+        <v>406.2</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5329,6 +6497,18 @@
       <c r="L97" t="n">
         <v>2472.6</v>
       </c>
+      <c r="M97" t="n">
+        <v>139.57</v>
+      </c>
+      <c r="N97" t="n">
+        <v>362.54</v>
+      </c>
+      <c r="O97" t="n">
+        <v>135.59</v>
+      </c>
+      <c r="P97" t="n">
+        <v>70.08</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5379,6 +6559,18 @@
       <c r="L98" t="n">
         <v>2050.1</v>
       </c>
+      <c r="M98" t="n">
+        <v>207.94</v>
+      </c>
+      <c r="N98" t="n">
+        <v>85.42</v>
+      </c>
+      <c r="O98" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="P98" t="n">
+        <v>262.12</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5429,6 +6621,18 @@
       <c r="L99" t="n">
         <v>65.40000000000001</v>
       </c>
+      <c r="M99" t="n">
+        <v>179.71</v>
+      </c>
+      <c r="N99" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="O99" t="n">
+        <v>211.42</v>
+      </c>
+      <c r="P99" t="n">
+        <v>252.43</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5479,6 +6683,18 @@
       <c r="L100" t="n">
         <v>1229</v>
       </c>
+      <c r="M100" t="n">
+        <v>442.15</v>
+      </c>
+      <c r="N100" t="n">
+        <v>76</v>
+      </c>
+      <c r="O100" t="n">
+        <v>455.75</v>
+      </c>
+      <c r="P100" t="n">
+        <v>417.55</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5529,6 +6745,18 @@
       <c r="L101" t="n">
         <v>7217</v>
       </c>
+      <c r="M101" t="n">
+        <v>478.89</v>
+      </c>
+      <c r="N101" t="n">
+        <v>452.47</v>
+      </c>
+      <c r="O101" t="n">
+        <v>409.58</v>
+      </c>
+      <c r="P101" t="n">
+        <v>402.44</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5579,6 +6807,18 @@
       <c r="L102" t="n">
         <v>128.9</v>
       </c>
+      <c r="M102" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="N102" t="n">
+        <v>403.35</v>
+      </c>
+      <c r="O102" t="n">
+        <v>129.68</v>
+      </c>
+      <c r="P102" t="n">
+        <v>413.29</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5629,6 +6869,18 @@
       <c r="L103" t="n">
         <v>1862.1</v>
       </c>
+      <c r="M103" t="n">
+        <v>88.52</v>
+      </c>
+      <c r="N103" t="n">
+        <v>73.51000000000001</v>
+      </c>
+      <c r="O103" t="n">
+        <v>75.11</v>
+      </c>
+      <c r="P103" t="n">
+        <v>292.24</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5679,6 +6931,18 @@
       <c r="L104" t="n">
         <v>62.1</v>
       </c>
+      <c r="M104" t="n">
+        <v>116.36</v>
+      </c>
+      <c r="N104" t="n">
+        <v>413.34</v>
+      </c>
+      <c r="O104" t="n">
+        <v>459.63</v>
+      </c>
+      <c r="P104" t="n">
+        <v>446.47</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5729,6 +6993,18 @@
       <c r="L105" t="n">
         <v>765.8</v>
       </c>
+      <c r="M105" t="n">
+        <v>117.05</v>
+      </c>
+      <c r="N105" t="n">
+        <v>490.16</v>
+      </c>
+      <c r="O105" t="n">
+        <v>285.51</v>
+      </c>
+      <c r="P105" t="n">
+        <v>341.61</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5779,6 +7055,18 @@
       <c r="L106" t="n">
         <v>141.4</v>
       </c>
+      <c r="M106" t="n">
+        <v>242.74</v>
+      </c>
+      <c r="N106" t="n">
+        <v>328.81</v>
+      </c>
+      <c r="O106" t="n">
+        <v>350.36</v>
+      </c>
+      <c r="P106" t="n">
+        <v>346.82</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5829,6 +7117,18 @@
       <c r="L107" t="n">
         <v>23.6</v>
       </c>
+      <c r="M107" t="n">
+        <v>294.77</v>
+      </c>
+      <c r="N107" t="n">
+        <v>175.53</v>
+      </c>
+      <c r="O107" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="P107" t="n">
+        <v>115.36</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5879,6 +7179,18 @@
       <c r="L108" t="n">
         <v>782.5</v>
       </c>
+      <c r="M108" t="n">
+        <v>131.74</v>
+      </c>
+      <c r="N108" t="n">
+        <v>274.56</v>
+      </c>
+      <c r="O108" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="P108" t="n">
+        <v>16.06</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5929,6 +7241,18 @@
       <c r="L109" t="n">
         <v>402.2</v>
       </c>
+      <c r="M109" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="N109" t="n">
+        <v>65.93000000000001</v>
+      </c>
+      <c r="O109" t="n">
+        <v>344.26</v>
+      </c>
+      <c r="P109" t="n">
+        <v>66.98</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5979,6 +7303,18 @@
       <c r="L110" t="n">
         <v>2042.8</v>
       </c>
+      <c r="M110" t="n">
+        <v>209.76</v>
+      </c>
+      <c r="N110" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="O110" t="n">
+        <v>212.95</v>
+      </c>
+      <c r="P110" t="n">
+        <v>180.67</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6029,6 +7365,18 @@
       <c r="L111" t="n">
         <v>298.9</v>
       </c>
+      <c r="M111" t="n">
+        <v>184.94</v>
+      </c>
+      <c r="N111" t="n">
+        <v>485.46</v>
+      </c>
+      <c r="O111" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="P111" t="n">
+        <v>52.91</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6079,6 +7427,18 @@
       <c r="L112" t="n">
         <v>411</v>
       </c>
+      <c r="M112" t="n">
+        <v>283.39</v>
+      </c>
+      <c r="N112" t="n">
+        <v>325.01</v>
+      </c>
+      <c r="O112" t="n">
+        <v>469.21</v>
+      </c>
+      <c r="P112" t="n">
+        <v>417.99</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6129,6 +7489,18 @@
       <c r="L113" t="n">
         <v>12733.2</v>
       </c>
+      <c r="M113" t="n">
+        <v>476.57</v>
+      </c>
+      <c r="N113" t="n">
+        <v>263.53</v>
+      </c>
+      <c r="O113" t="n">
+        <v>317.4</v>
+      </c>
+      <c r="P113" t="n">
+        <v>279.48</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6179,6 +7551,18 @@
       <c r="L114" t="n">
         <v>338.3</v>
       </c>
+      <c r="M114" t="n">
+        <v>345.4</v>
+      </c>
+      <c r="N114" t="n">
+        <v>466.85</v>
+      </c>
+      <c r="O114" t="n">
+        <v>400.91</v>
+      </c>
+      <c r="P114" t="n">
+        <v>314.07</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6229,6 +7613,18 @@
       <c r="L115" t="n">
         <v>2822</v>
       </c>
+      <c r="M115" t="n">
+        <v>257.99</v>
+      </c>
+      <c r="N115" t="n">
+        <v>217.19</v>
+      </c>
+      <c r="O115" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="P115" t="n">
+        <v>313.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6279,6 +7675,18 @@
       <c r="L116" t="n">
         <v>5209.8</v>
       </c>
+      <c r="M116" t="n">
+        <v>308.99</v>
+      </c>
+      <c r="N116" t="n">
+        <v>435.94</v>
+      </c>
+      <c r="O116" t="n">
+        <v>428.19</v>
+      </c>
+      <c r="P116" t="n">
+        <v>340.49</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6329,6 +7737,18 @@
       <c r="L117" t="n">
         <v>8452.200000000001</v>
       </c>
+      <c r="M117" t="n">
+        <v>338.26</v>
+      </c>
+      <c r="N117" t="n">
+        <v>413.16</v>
+      </c>
+      <c r="O117" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="P117" t="n">
+        <v>244.9</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6379,6 +7799,18 @@
       <c r="L118" t="n">
         <v>5452.7</v>
       </c>
+      <c r="M118" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="N118" t="n">
+        <v>105.92</v>
+      </c>
+      <c r="O118" t="n">
+        <v>431.46</v>
+      </c>
+      <c r="P118" t="n">
+        <v>2.16</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6429,6 +7861,18 @@
       <c r="L119" t="n">
         <v>244.2</v>
       </c>
+      <c r="M119" t="n">
+        <v>449.82</v>
+      </c>
+      <c r="N119" t="n">
+        <v>126.29</v>
+      </c>
+      <c r="O119" t="n">
+        <v>227.16</v>
+      </c>
+      <c r="P119" t="n">
+        <v>398.95</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6479,6 +7923,18 @@
       <c r="L120" t="n">
         <v>0</v>
       </c>
+      <c r="M120" t="n">
+        <v>390.09</v>
+      </c>
+      <c r="N120" t="n">
+        <v>146.84</v>
+      </c>
+      <c r="O120" t="n">
+        <v>169.91</v>
+      </c>
+      <c r="P120" t="n">
+        <v>374.26</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6529,6 +7985,18 @@
       <c r="L121" t="n">
         <v>168.2</v>
       </c>
+      <c r="M121" t="n">
+        <v>437.32</v>
+      </c>
+      <c r="N121" t="n">
+        <v>120.65</v>
+      </c>
+      <c r="O121" t="n">
+        <v>276.76</v>
+      </c>
+      <c r="P121" t="n">
+        <v>251.73</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6578,6 +8046,18 @@
       </c>
       <c r="L122" t="n">
         <v>5751.6</v>
+      </c>
+      <c r="M122" t="n">
+        <v>399.04</v>
+      </c>
+      <c r="N122" t="n">
+        <v>293.43</v>
+      </c>
+      <c r="O122" t="n">
+        <v>463.37</v>
+      </c>
+      <c r="P122" t="n">
+        <v>267.83</v>
       </c>
     </row>
   </sheetData>
